--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486285_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486285_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.297</v>
+        <v>7.0187</v>
       </c>
       <c r="E2" t="n">
-        <v>8.121600000000001</v>
+        <v>7.9666</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8246</v>
+        <v>-0.9479</v>
       </c>
       <c r="G2" t="n">
         <v>3.3031</v>
@@ -610,13 +610,13 @@
         <v>3.9151</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2963</v>
+        <v>0.018</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7487</v>
+        <v>0.5936</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4523</v>
+        <v>-0.5756</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3741</v>
+        <v>3.7393</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9227</v>
+        <v>4.1029</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5486</v>
+        <v>-0.3636</v>
       </c>
       <c r="G3" t="n">
         <v>0.6698</v>
@@ -688,13 +688,13 @@
         <v>3.6976</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3201</v>
+        <v>0.0451</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6117</v>
+        <v>0.7919</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9318</v>
+        <v>-0.7469</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0207</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3284</v>
+        <v>2.2466</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2637</v>
+        <v>3.9969</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9353</v>
+        <v>-1.7504</v>
       </c>
       <c r="G4" t="n">
         <v>-1.288</v>
@@ -766,13 +766,13 @@
         <v>4.3501</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0786</v>
+        <v>-0.1604</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3003</v>
+        <v>1.0335</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.3788</v>
+        <v>-1.1939</v>
       </c>
       <c r="V4" t="n">
         <v>2.8249</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. MENUGE</t>
+          <t>J. MARTINEZ CABEZUDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5406</v>
+        <v>0.5634</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5163</v>
+        <v>0.2797</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9757</v>
+        <v>0.2837</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0747</v>
+        <v>0.2542</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2684</v>
+        <v>-0.5992</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1937</v>
+        <v>0.8534</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2387</v>
+        <v>0.9022</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1095</v>
+        <v>0.3467</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1292</v>
+        <v>0.5554</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3134</v>
+        <v>-0.6479</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3779</v>
+        <v>-0.9459</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0645</v>
+        <v>0.298</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.435</v>
       </c>
       <c r="R5" t="n">
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2227</v>
+        <v>-0.5831</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2776</v>
+        <v>-0.1875</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0549</v>
+        <v>-0.3957</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTINEZ CABEZUDO</t>
+          <t>L. MENUGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3091</v>
+        <v>0.1013</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0562</v>
+        <v>1.2927</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2529</v>
+        <v>-1.1915</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2542</v>
+        <v>-0.0747</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5992</v>
+        <v>-1.2684</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8534</v>
+        <v>1.1937</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9022</v>
+        <v>1.2387</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3467</v>
+        <v>0.1095</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5554</v>
+        <v>1.1292</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6479</v>
+        <v>-1.3134</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9459</v>
+        <v>-1.3779</v>
       </c>
       <c r="O6" t="n">
-        <v>0.298</v>
+        <v>0.0645</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8375</v>
+        <v>-0.2166</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.411</v>
+        <v>0.0541</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4265</v>
+        <v>-0.2707</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6082</v>
+        <v>-0.3423</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5694</v>
+        <v>0.6811</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1775</v>
+        <v>-1.0234</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6943</v>
@@ -1000,13 +1000,13 @@
         <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5017</v>
+        <v>-0.2358</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1406</v>
+        <v>0.2524</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6423</v>
+        <v>-0.4882</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9347</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0916</v>
+        <v>-1.7225</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4618</v>
+        <v>-1.7228</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3702</v>
+        <v>0.0003</v>
       </c>
       <c r="G8" t="n">
         <v>-1.958</v>
@@ -1078,13 +1078,13 @@
         <v>3.4801</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1336</v>
+        <v>0.2355</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0529</v>
+        <v>0.6862</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0808</v>
+        <v>-0.4506</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.458</v>
+        <v>-3.2094</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.858</v>
+        <v>-2.8668</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4</v>
+        <v>-0.3425</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.98</v>
+        <v>-5.6431</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0103</v>
+        <v>-1.8979</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0303</v>
+        <v>-3.7452</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0651</v>
+        <v>-2.2985</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1799</v>
+        <v>-0.1032</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1147</v>
+        <v>-2.1953</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9149</v>
+        <v>-3.3447</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8304</v>
+        <v>-1.7948</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-1.5499</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.8276</v>
+        <v>3.0451</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.6976</v>
+        <v>-0.6525</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>3.6976</v>
       </c>
       <c r="S9" t="n">
-        <v>1.61</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9047</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2947</v>
+        <v>-0.6955</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3877</v>
+        <v>-3.749</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8294</v>
+        <v>-4.0874</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5583</v>
+        <v>0.3384</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.6431</v>
+        <v>-1.98</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8979</v>
+        <v>-2.0103</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.7452</v>
+        <v>0.0303</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2985</v>
+        <v>-1.0651</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1032</v>
+        <v>-1.1799</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1953</v>
+        <v>0.1147</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.3447</v>
+        <v>-0.9149</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7948</v>
+        <v>-0.8304</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5499</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0451</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.6525</v>
+        <v>-3.6976</v>
       </c>
       <c r="R10" t="n">
-        <v>3.6976</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7897</v>
+        <v>0.3191</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8784</v>
+        <v>0.6754</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9113</v>
+        <v>-0.3563</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.303699999999998</v>
+        <v>4.646099999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>9.300700000000001</v>
+        <v>9.642900000000001</v>
       </c>
       <c r="F11" t="n">
         <v>-4.9969</v>
@@ -1288,7 +1288,7 @@
         <v>13.7992</v>
       </c>
       <c r="K11" t="n">
-        <v>5.005599999999998</v>
+        <v>5.005599999999999</v>
       </c>
       <c r="L11" t="n">
         <v>8.7935</v>
@@ -1300,7 +1300,7 @@
         <v>-14.9509</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.2594</v>
+        <v>-6.259399999999999</v>
       </c>
       <c r="P11" t="n">
         <v>11.9627</v>
@@ -1312,10 +1312,10 @@
         <v>25.0131</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5322</v>
+        <v>-1.1896</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6413</v>
+        <v>3.9837</v>
       </c>
       <c r="U11" t="n">
         <v>-5.1734</v>
@@ -1327,13 +1327,13 @@
         <v>4.9103</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.6266</v>
+        <v>-3.626599999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>S. THRASTARSON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.2011</v>
+        <v>3.5453</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1419</v>
+        <v>3.2766</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0592</v>
+        <v>0.2687</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7278</v>
+        <v>3.4724</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6618</v>
+        <v>3.1114</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9339</v>
+        <v>0.3609</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2666</v>
+        <v>4.5324</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2666</v>
+        <v>3.7292</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.8032</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-1.0601</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3951</v>
+        <v>-0.6178</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9339</v>
+        <v>-0.4423</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2175</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8</v>
+        <v>-0.0772</v>
       </c>
       <c r="T12" t="n">
-        <v>2.0297</v>
+        <v>0.1166</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2297</v>
+        <v>-0.1938</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1093</v>
+        <v>1.8902</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0207</v>
+        <v>1.8902</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. THRASTARSON</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.9184</v>
+        <v>2.2017</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8295</v>
+        <v>2.0243</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1773</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4724</v>
+        <v>2.7278</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1114</v>
+        <v>3.6618</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3609</v>
+        <v>-0.9339</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5324</v>
+        <v>3.2666</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7292</v>
+        <v>3.2666</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8032</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0601</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6178</v>
+        <v>0.3951</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4423</v>
+        <v>-0.9339</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.7401</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7040999999999999</v>
+        <v>0.8006</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3305</v>
+        <v>0.9121</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3736</v>
+        <v>-0.1115</v>
       </c>
       <c r="V13" t="n">
-        <v>1.8902</v>
+        <v>-1.1093</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8902</v>
+        <v>0.0207</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4777</v>
+        <v>1.8314</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0497</v>
+        <v>3.3478</v>
       </c>
       <c r="F14" t="n">
-        <v>0.428</v>
+        <v>-1.5164</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7973</v>
+        <v>-1.0369</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7025</v>
+        <v>0.7362</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0948</v>
+        <v>-1.773</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4501</v>
+        <v>1.2192</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3354</v>
+        <v>1.1045</v>
       </c>
       <c r="L14" t="n">
         <v>0.1147</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6528</v>
+        <v>-2.2561</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6328</v>
+        <v>-0.3683</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0199</v>
+        <v>-1.8878</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2023</v>
+        <v>0.846</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2966</v>
+        <v>0.9986</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9056999999999999</v>
+        <v>-0.1526</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7395</v>
+        <v>0.9347</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3041</v>
+        <v>1.0982</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2419</v>
+        <v>1.3791</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9377</v>
+        <v>-0.2809</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0369</v>
+        <v>0.7973</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7362</v>
+        <v>0.7025</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.773</v>
+        <v>0.0948</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2192</v>
+        <v>1.4501</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1045</v>
+        <v>1.3354</v>
       </c>
       <c r="L15" t="n">
         <v>0.1147</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2561</v>
+        <v>-0.6528</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3683</v>
+        <v>-0.6328</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8878</v>
+        <v>-0.0199</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3187</v>
+        <v>0.8229</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8927</v>
+        <v>0.6261</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5739</v>
+        <v>0.1968</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9347</v>
+        <v>-0.7395</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.031</v>
+        <v>0.876</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1538</v>
+        <v>1.8244</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1848</v>
+        <v>-0.9484</v>
       </c>
       <c r="G16" t="n">
         <v>2.3411</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1322</v>
+        <v>-0.2253</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.399</v>
+        <v>0.2716</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7333</v>
+        <v>-0.4969</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3698</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1375</v>
+        <v>0.2954</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6993</v>
+        <v>-0.3111</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8368</v>
+        <v>0.6065</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1687</v>
+        <v>-0.6714</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2348</v>
+        <v>0.1398</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9339</v>
+        <v>-0.8112</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6538</v>
+        <v>0.5168</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6538</v>
+        <v>0.0762</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.4407</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5149</v>
+        <v>-1.1882</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.581</v>
+        <v>0.0636</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9339</v>
+        <v>-1.2519</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5962</v>
+        <v>-0.1208</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3531</v>
+        <v>0.2596</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2431</v>
+        <v>-0.3803</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6834</v>
+        <v>-0.912</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9817</v>
+        <v>0.1405</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2983</v>
+        <v>-1.0525</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6714</v>
+        <v>-2.1687</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1398</v>
+        <v>-1.2348</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8112</v>
+        <v>-0.9339</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5168</v>
+        <v>-0.6538</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0762</v>
+        <v>-0.6538</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4407</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1882</v>
+        <v>-1.5149</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0636</v>
+        <v>-0.581</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2519</v>
+        <v>-0.9339</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1751</v>
+        <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0996</v>
+        <v>0.8217</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.411</v>
+        <v>0.7943</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6886</v>
+        <v>0.0273</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1582</v>
+        <v>-2.1537</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6074</v>
+        <v>-1.9368</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.2169</v>
       </c>
       <c r="G19" t="n">
         <v>2.5156</v>
@@ -1936,13 +1936,13 @@
         <v>2.3926</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9762999999999999</v>
+        <v>0.0282</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4675</v>
+        <v>0.2031</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5088</v>
+        <v>-0.1749</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5649999999999999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8553</v>
+        <v>-3.5213</v>
       </c>
       <c r="E20" t="n">
         <v>-0.9994</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8559</v>
+        <v>-2.522</v>
       </c>
       <c r="G20" t="n">
         <v>-0.288</v>
@@ -2014,13 +2014,13 @@
         <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3922</v>
+        <v>-0.0583</v>
       </c>
       <c r="T20" t="n">
         <v>0.4146</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8068</v>
+        <v>-0.4729</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5649999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.3395</v>
+        <v>-6.0743</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5308</v>
+        <v>-3.7485</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8087</v>
+        <v>-2.3257</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2783</v>
@@ -2092,13 +2092,13 @@
         <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0808</v>
+        <v>0.1845</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2055</v>
+        <v>0.5768</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8753</v>
+        <v>-0.3924</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7602</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.303599999999999</v>
+        <v>-2.8133</v>
       </c>
       <c r="E22" t="n">
-        <v>4.996800000000001</v>
+        <v>4.9969</v>
       </c>
       <c r="F22" t="n">
-        <v>-9.3004</v>
+        <v>-7.8103</v>
       </c>
       <c r="G22" t="n">
         <v>7.4109</v>
@@ -2170,13 +2170,13 @@
         <v>13.0503</v>
       </c>
       <c r="S22" t="n">
-        <v>1.532</v>
+        <v>3.0223</v>
       </c>
       <c r="T22" t="n">
-        <v>5.1732</v>
+        <v>5.173400000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.6412</v>
+        <v>-2.1512</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2839</v>
